--- a/docs/Sprint Retrspectives.xlsx
+++ b/docs/Sprint Retrspectives.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data\Laravel_Dev\Examen-Grado\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871FC9F3-8ED4-420C-A072-4E2162DC93E0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F49AC7-C366-4EF4-B819-4BFD8D5D075D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Retrospective - 1" sheetId="1" r:id="rId1"/>
@@ -100,10 +100,10 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -138,7 +138,7 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -179,7 +179,7 @@
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
@@ -1982,13 +1982,6 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 4'!$D$6:$D$9</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>'Sprint Retrospective - 4'!$D$6:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
@@ -2010,28 +2003,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 4'!$E$6:$E$9</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sprint Retrospective - 4'!$E$6:$E$9</c:f>
+              <c:f>'Sprint Retrospective - 4'!$G$6:$G$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2071,13 +2057,6 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 4'!$D$6:$D$9</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>'Sprint Retrospective - 4'!$D$6:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
@@ -2099,28 +2078,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 4'!$F$6:$F$9</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sprint Retrospective - 4'!$F$6:$F$9</c:f>
+              <c:f>'Sprint Retrospective - 4'!$H$6:$H$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2182,9 +2154,6 @@
                   <c:numRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>'Sprint Retrospective - 4'!$D$6:$D$9</c15:sqref>
-                        </c15:fullRef>
                         <c15:formulaRef>
                           <c15:sqref>'Sprint Retrospective - 4'!$D$6:$D$9</c15:sqref>
                         </c15:formulaRef>
@@ -2212,9 +2181,6 @@
                   <c:numRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>'Sprint Retrospective - 4'!$D$6:$D$9</c15:sqref>
-                        </c15:fullRef>
                         <c15:formulaRef>
                           <c15:sqref>'Sprint Retrospective - 4'!$D$6:$D$9</c15:sqref>
                         </c15:formulaRef>
@@ -2370,8 +2336,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.18527143482064742"/>
-          <c:y val="3.7615193934091573E-2"/>
+          <c:x val="0.69149540954683564"/>
+          <c:y val="6.076334208223972E-2"/>
           <c:w val="0.26279046369203851"/>
           <c:h val="0.21238480606590843"/>
         </c:manualLayout>
@@ -2602,31 +2568,31 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 5'!$E$5:$E$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 5'!$G$6:$G$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 5'!$E$5:$E$10</c:f>
+              <c:f>'Sprint Retrospective - 5'!$G$6:$G$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>33</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2703,31 +2669,31 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 5'!$F$5:$F$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 5'!$H$6:$H$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 5'!$F$5:$F$10</c:f>
+              <c:f>'Sprint Retrospective - 5'!$H$6:$H$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>34</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2826,33 +2792,33 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>'Sprint Retrospective - 5'!$D$5:$D$11</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 5'!$D$5:$D$10</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
                       <c:ptCount val="6"/>
-                      <c:pt idx="0" formatCode="General">
-                        <c:v>0</c:v>
+                      <c:pt idx="0">
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3</c:v>
+                        <c:v>6</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>6</c:v>
+                        <c:v>9</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>9</c:v>
+                        <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>13</c:v>
+                        <c:v>16</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>16</c:v>
+                        <c:v>19</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2989,8 +2955,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.18527143482064742"/>
-          <c:y val="3.7615193934091573E-2"/>
+          <c:x val="0.661066640528855"/>
+          <c:y val="5.1504082822980461E-2"/>
           <c:w val="0.26279046369203851"/>
           <c:h val="0.21238480606590843"/>
         </c:manualLayout>
@@ -6790,11 +6756,11 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6928,7 +6894,7 @@
       <c r="C10" s="3">
         <v>45926</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>15</v>
       </c>
       <c r="E10">
@@ -6945,7 +6911,7 @@
       <c r="C11" s="3">
         <v>45928</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>17</v>
       </c>
       <c r="E11">
@@ -7068,12 +7034,12 @@
     <row r="10" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="6"/>
+      <c r="D11" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7084,7 +7050,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034617F5-103B-4443-918E-9BF8CADC758F}">
-  <dimension ref="B2:F11"/>
+  <dimension ref="B2:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -7094,14 +7060,14 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -7118,7 +7084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>0</v>
       </c>
@@ -7129,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>45912</v>
       </c>
@@ -7143,10 +7109,16 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>45915</v>
       </c>
@@ -7160,10 +7132,16 @@
         <v>16</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>45919</v>
       </c>
@@ -7177,10 +7155,16 @@
         <v>24</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>45922</v>
       </c>
@@ -7194,17 +7178,23 @@
         <v>32</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>45925</v>
       </c>
       <c r="C10" s="3">
         <v>45926</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>15</v>
       </c>
       <c r="E10">
@@ -7213,15 +7203,21 @@
       <c r="F10">
         <v>27</v>
       </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>45927</v>
       </c>
       <c r="C11" s="3">
         <v>45928</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>17</v>
       </c>
       <c r="E11">
@@ -7240,7 +7236,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC44D17D-F45F-4D39-9789-8C8C574CB691}">
-  <dimension ref="B2:F11"/>
+  <dimension ref="B2:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -7250,14 +7246,14 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -7274,7 +7270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>0</v>
       </c>
@@ -7285,7 +7281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>45912</v>
       </c>
@@ -7301,8 +7297,14 @@
       <c r="F6">
         <v>6</v>
       </c>
+      <c r="G6">
+        <v>33</v>
+      </c>
+      <c r="H6">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>45915</v>
       </c>
@@ -7318,8 +7320,14 @@
       <c r="F7">
         <v>14</v>
       </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>34</v>
+      </c>
     </row>
-    <row r="8" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>45919</v>
       </c>
@@ -7335,8 +7343,14 @@
       <c r="F8">
         <v>20</v>
       </c>
+      <c r="G8">
+        <v>23</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
     </row>
-    <row r="9" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>45922</v>
       </c>
@@ -7352,32 +7366,44 @@
       <c r="F9">
         <v>24</v>
       </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
     </row>
-    <row r="10" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>45925</v>
       </c>
       <c r="C10" s="3">
         <v>45926</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>16</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>34</v>
       </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
     </row>
-    <row r="11" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>45927</v>
       </c>
       <c r="C11" s="3">
         <v>45928</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>19</v>
       </c>
       <c r="E11">
@@ -7385,6 +7411,12 @@
       </c>
       <c r="F11">
         <v>35</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Sprint Retrspectives.xlsx
+++ b/docs/Sprint Retrspectives.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data\Laravel_Dev\Examen-Grado\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F49AC7-C366-4EF4-B819-4BFD8D5D075D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A222C1E-EFBF-4166-B914-1815A79E25AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Retrospective - 1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Sprint Retrospective - 3" sheetId="4" r:id="rId3"/>
     <sheet name="Sprint Retrospective - 4" sheetId="5" r:id="rId4"/>
     <sheet name="Sprint Retrospective - 5" sheetId="3" r:id="rId5"/>
+    <sheet name="Sprint Retrospective - 5 (2)" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="6">
   <si>
     <t>Dias</t>
   </si>
@@ -240,20 +241,23 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 1'!$D$6:$D$9</c:f>
+              <c:f>'Sprint Retrospective - 1'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+                <c:ptCount val="5"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
@@ -261,24 +265,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 1'!$E$5:$E$9</c:f>
+              <c:f>'Sprint Retrospective - 1'!$G$5:$G$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -318,20 +322,23 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 1'!$D$6:$D$9</c:f>
+              <c:f>'Sprint Retrospective - 1'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+                <c:ptCount val="5"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
@@ -339,24 +346,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 1'!$F$5:$F$9</c:f>
+              <c:f>'Sprint Retrospective - 1'!$H$5:$H$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -419,23 +426,26 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 1'!$D$6:$D$9</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 1'!$D$5:$D$9</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0" formatCode="General">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
                         <c:v>2</c:v>
                       </c:pt>
-                      <c:pt idx="1">
+                      <c:pt idx="2">
                         <c:v>5</c:v>
                       </c:pt>
-                      <c:pt idx="2">
+                      <c:pt idx="3">
                         <c:v>8</c:v>
                       </c:pt>
-                      <c:pt idx="3">
+                      <c:pt idx="4">
                         <c:v>11</c:v>
                       </c:pt>
                     </c:numCache>
@@ -489,7 +499,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -603,8 +613,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.18527143482064742"/>
-          <c:y val="3.7615193934091573E-2"/>
+          <c:x val="0.68872915781792832"/>
+          <c:y val="3.2985564304461944E-2"/>
           <c:w val="0.26279046369203851"/>
           <c:h val="0.21238480606590843"/>
         </c:manualLayout>
@@ -801,31 +811,34 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 2'!$D$6:$D$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 2'!$D$5:$D$12</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 2'!$D$6:$D$11</c:f>
+              <c:f>('Sprint Retrospective - 2'!$D$5:$D$10,'Sprint Retrospective - 2'!$D$12)</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
+                <c:ptCount val="7"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>17</c:v>
+                <c:pt idx="6">
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -835,31 +848,34 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 2'!$E$5:$E$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 2'!$G$5:$G$12</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 2'!$E$5:$E$10</c:f>
+              <c:f>('Sprint Retrospective - 2'!$G$5:$G$10,'Sprint Retrospective - 2'!$G$12)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -902,31 +918,34 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 2'!$D$6:$D$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 2'!$D$5:$D$12</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 2'!$D$6:$D$11</c:f>
+              <c:f>('Sprint Retrospective - 2'!$D$5:$D$10,'Sprint Retrospective - 2'!$D$12)</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
+                <c:ptCount val="7"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>17</c:v>
+                <c:pt idx="6">
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -936,31 +955,34 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 2'!$F$5:$F$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 2'!$H$5:$H$12</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 2'!$F$5:$F$10</c:f>
+              <c:f>('Sprint Retrospective - 2'!$H$5:$H$10,'Sprint Retrospective - 2'!$H$12)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1023,33 +1045,36 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>'Sprint Retrospective - 2'!$D$6:$D$11</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 2'!$D$5:$D$12</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 2'!$D$6:$D$11</c15:sqref>
+                          <c15:sqref>('Sprint Retrospective - 2'!$D$5:$D$10,'Sprint Retrospective - 2'!$D$12)</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="6"/>
-                      <c:pt idx="0">
+                      <c:ptCount val="7"/>
+                      <c:pt idx="0" formatCode="General">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
                         <c:v>3</c:v>
                       </c:pt>
-                      <c:pt idx="1">
+                      <c:pt idx="2">
                         <c:v>7</c:v>
                       </c:pt>
-                      <c:pt idx="2">
+                      <c:pt idx="3">
                         <c:v>10</c:v>
                       </c:pt>
-                      <c:pt idx="3">
+                      <c:pt idx="4">
                         <c:v>13</c:v>
                       </c:pt>
-                      <c:pt idx="4">
+                      <c:pt idx="5">
                         <c:v>15</c:v>
                       </c:pt>
-                      <c:pt idx="5">
-                        <c:v>17</c:v>
+                      <c:pt idx="6">
+                        <c:v>19</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1108,7 +1133,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1222,8 +1247,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.18527143482064742"/>
-          <c:y val="3.7615193934091573E-2"/>
+          <c:x val="0.68319665436011356"/>
+          <c:y val="5.6133712452610091E-2"/>
           <c:w val="0.26279046369203851"/>
           <c:h val="0.21238480606590843"/>
         </c:manualLayout>
@@ -1420,21 +1445,24 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 3'!$D$6:$D$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 3'!$D$5:$D$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 3'!$D$6:$D$8</c:f>
+              <c:f>'Sprint Retrospective - 3'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
+                <c:ptCount val="4"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
@@ -1445,22 +1473,25 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 3'!$E$5:$E$8</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 3'!$G$5:$G$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 3'!$E$5:$E$7</c:f>
+              <c:f>'Sprint Retrospective - 3'!$G$5:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1503,21 +1534,24 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 3'!$D$6:$D$11</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 3'!$D$5:$D$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 3'!$D$6:$D$8</c:f>
+              <c:f>'Sprint Retrospective - 3'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
+                <c:ptCount val="4"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
@@ -1528,22 +1562,25 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 3'!$F$5:$F$8</c15:sqref>
+                    <c15:sqref>'Sprint Retrospective - 3'!$H$5:$H$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Sprint Retrospective - 3'!$F$5:$F$7</c:f>
+              <c:f>'Sprint Retrospective - 3'!$H$5:$H$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1606,23 +1643,26 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>'Sprint Retrospective - 3'!$D$6:$D$11</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 3'!$D$5:$D$8</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 3'!$D$6:$D$8</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 3'!$D$5:$D$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="3"/>
-                      <c:pt idx="0">
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0" formatCode="General">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
                         <c:v>2</c:v>
                       </c:pt>
-                      <c:pt idx="1">
+                      <c:pt idx="2">
                         <c:v>6</c:v>
                       </c:pt>
-                      <c:pt idx="2">
+                      <c:pt idx="3">
                         <c:v>9</c:v>
                       </c:pt>
                     </c:numCache>
@@ -1636,13 +1676,13 @@
                           <c15:sqref>'Sprint Retrospective - 3'!$D$5:$D$8</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 3'!$D$5:$D$7</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 3'!$D$5:$D$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="3"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0" formatCode="General">
                         <c:v>0</c:v>
                       </c:pt>
@@ -1651,6 +1691,9 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>9</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1673,7 +1716,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1787,8 +1830,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.18527143482064742"/>
-          <c:y val="3.7615193934091573E-2"/>
+          <c:x val="0.65000163361322572"/>
+          <c:y val="6.076334208223972E-2"/>
           <c:w val="0.26279046369203851"/>
           <c:h val="0.21238480606590843"/>
         </c:manualLayout>
@@ -1982,42 +2025,42 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 4'!$D$6:$D$9</c:f>
+              <c:f>'Sprint Retrospective - 4'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="4"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 4'!$G$6:$G$9</c:f>
+              <c:f>'Sprint Retrospective - 4'!$G$5:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>32</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2057,42 +2100,42 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 4'!$D$6:$D$9</c:f>
+              <c:f>'Sprint Retrospective - 4'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="4"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint Retrospective - 4'!$H$6:$H$9</c:f>
+              <c:f>'Sprint Retrospective - 4'!$H$5:$H$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>32</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2155,24 +2198,24 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 4'!$D$6:$D$9</c15:sqref>
+                          <c15:sqref>'Sprint Retrospective - 4'!$D$5:$D$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
                       <c:ptCount val="4"/>
-                      <c:pt idx="0">
+                      <c:pt idx="0" formatCode="General">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
                         <c:v>2</c:v>
                       </c:pt>
-                      <c:pt idx="1">
+                      <c:pt idx="2">
                         <c:v>7</c:v>
                       </c:pt>
-                      <c:pt idx="2">
+                      <c:pt idx="3">
                         <c:v>10</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>14</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2222,7 +2265,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2505,7 +2548,7 @@
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>'Sprint Retrospective - 5'!$E$4</c:f>
@@ -2531,68 +2574,48 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sprint Retrospective - 5'!$D$6:$D$11</c:f>
+              <c:f>'Sprint Retrospective - 5'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
+                <c:ptCount val="5"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>9</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 5'!$G$6:$G$11</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sprint Retrospective - 5'!$G$6:$G$11</c:f>
+              <c:f>'Sprint Retrospective - 5'!$G$5:$G$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>33</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>23</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2606,7 +2629,7 @@
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
               <c:f>'Sprint Retrospective - 5'!$F$4</c:f>
@@ -2632,68 +2655,48 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sprint Retrospective - 5'!$D$6:$D$11</c:f>
+              <c:f>'Sprint Retrospective - 5'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
+                <c:ptCount val="5"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>9</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Sprint Retrospective - 5'!$H$6:$H$11</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Sprint Retrospective - 5'!$H$6:$H$11</c:f>
+              <c:f>'Sprint Retrospective - 5'!$H$5:$H$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>34</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2716,123 +2719,7 @@
         <c:smooth val="0"/>
         <c:axId val="871392544"/>
         <c:axId val="839321808"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="0"/>
-                <c:order val="0"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 5'!$D$4</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Dias</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="28575" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent1"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="none"/>
-                </c:marker>
-                <c:cat>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="6"/>
-                      <c:pt idx="0">
-                        <c:v>3</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>6</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>9</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>13</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>16</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>19</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>'Sprint Retrospective - 5'!$D$6:$D$11</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="6"/>
-                      <c:pt idx="0">
-                        <c:v>3</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>6</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>9</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>13</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>16</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>19</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000002-ECE2-4501-AD13-B73BAA6235FF}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
+        <c:extLst/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="871392544"/>
@@ -2841,7 +2728,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2975,6 +2862,555 @@
         <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-419"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-419"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-419" sz="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Puntos HU</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.4874890638670166E-2"/>
+          <c:y val="0.32407407407407407"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-419"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17213648293963255"/>
+          <c:y val="9.7361111111111107E-2"/>
+          <c:w val="0.79730796150481187"/>
+          <c:h val="0.68933617672790903"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint Retrospective - 5 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Progreso Esperado</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint Retrospective - 5 (2)'!$D$6:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint Retrospective - 5 (2)'!$G$6:$G$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F1E9-4381-8DFA-EEB22E41BBDC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint Retrospective - 5 (2)'!$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Progreso Real</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint Retrospective - 5 (2)'!$D$6:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint Retrospective - 5 (2)'!$H$6:$H$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F1E9-4381-8DFA-EEB22E41BBDC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="871392544"/>
+        <c:axId val="839321808"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Sprint Retrospective - 5 (2)'!$D$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dias</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Sprint Retrospective - 5 (2)'!$D$6:$D$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0</c:formatCode>
+                      <c:ptCount val="6"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>18</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Sprint Retrospective - 5 (2)'!$D$6:$D$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0</c:formatCode>
+                      <c:ptCount val="6"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>18</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-F1E9-4381-8DFA-EEB22E41BBDC}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="871392544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="839321808"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="839321808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="871392544"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.20740135698805282"/>
+          <c:y val="0.89409667541557303"/>
+          <c:w val="0.58644188148680587"/>
+          <c:h val="6.4236657917760273E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3231,6 +3667,43 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -5296,6 +5769,522 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6324,6 +7313,120 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F786ACD0-DA71-472C-B5C9-5295D5FEA30B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6972300" y="4876800"/>
+          <a:ext cx="1257300" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-419" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Días</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>524554</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>113618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>217033</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>183015</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5842D6A2-E6EB-4808-88FB-19AC7ADE22BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="CuadroTexto 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DDB8990-134C-421D-A595-0BE4B2E7A06F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6642,7 +7745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F10"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -6652,14 +7755,14 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -6676,7 +7779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>0</v>
       </c>
@@ -6686,8 +7789,14 @@
       <c r="F5">
         <v>0</v>
       </c>
+      <c r="G5">
+        <v>47</v>
+      </c>
+      <c r="H5">
+        <v>47</v>
+      </c>
     </row>
-    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>45901</v>
       </c>
@@ -6703,8 +7812,14 @@
       <c r="F6">
         <v>4</v>
       </c>
+      <c r="G6">
+        <v>34</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>45538</v>
       </c>
@@ -6720,8 +7835,14 @@
       <c r="F7">
         <v>10</v>
       </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
     </row>
-    <row r="8" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>45906</v>
       </c>
@@ -6737,8 +7858,14 @@
       <c r="F8">
         <v>15</v>
       </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>45909</v>
       </c>
@@ -6754,8 +7881,14 @@
       <c r="F9">
         <v>19</v>
       </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
@@ -6774,7 +7907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F8AC47-9F24-4081-AEB7-F45A56AEE216}">
-  <dimension ref="B2:F11"/>
+  <dimension ref="B2:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -6784,14 +7917,14 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -6808,7 +7941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>0</v>
       </c>
@@ -6818,8 +7951,14 @@
       <c r="F5">
         <v>0</v>
       </c>
+      <c r="G5">
+        <v>83</v>
+      </c>
+      <c r="H5">
+        <v>82</v>
+      </c>
     </row>
-    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>45912</v>
       </c>
@@ -6835,8 +7974,14 @@
       <c r="F6">
         <v>6</v>
       </c>
+      <c r="G6">
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>74</v>
+      </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>45915</v>
       </c>
@@ -6852,8 +7997,14 @@
       <c r="F7">
         <v>14</v>
       </c>
+      <c r="G7">
+        <v>67</v>
+      </c>
+      <c r="H7">
+        <v>69</v>
+      </c>
     </row>
-    <row r="8" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>45919</v>
       </c>
@@ -6869,8 +8020,14 @@
       <c r="F8">
         <v>20</v>
       </c>
+      <c r="G8">
+        <v>59</v>
+      </c>
+      <c r="H8">
+        <v>54</v>
+      </c>
     </row>
-    <row r="9" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>45922</v>
       </c>
@@ -6886,8 +8043,14 @@
       <c r="F9">
         <v>24</v>
       </c>
+      <c r="G9">
+        <v>46</v>
+      </c>
+      <c r="H9">
+        <v>47</v>
+      </c>
     </row>
-    <row r="10" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>45925</v>
       </c>
@@ -6903,8 +8066,14 @@
       <c r="F10">
         <v>27</v>
       </c>
+      <c r="G10">
+        <v>33</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
     </row>
-    <row r="11" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>45927</v>
       </c>
@@ -6919,6 +8088,23 @@
       </c>
       <c r="F11">
         <v>30</v>
+      </c>
+      <c r="G11">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D12" s="5">
+        <v>19</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6930,7 +8116,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014D309F-8AD8-4499-A964-7E4C9CD619DE}">
-  <dimension ref="B2:F11"/>
+  <dimension ref="B2:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -6940,14 +8126,14 @@
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -6964,7 +8150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>0</v>
       </c>
@@ -6974,8 +8160,14 @@
       <c r="F5">
         <v>0</v>
       </c>
+      <c r="G5">
+        <v>41</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
     </row>
-    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>45929</v>
       </c>
@@ -6991,8 +8183,14 @@
       <c r="F6">
         <v>4</v>
       </c>
+      <c r="G6">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>45931</v>
       </c>
@@ -7008,8 +8206,14 @@
       <c r="F7">
         <v>17</v>
       </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
     </row>
-    <row r="8" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>45935</v>
       </c>
@@ -7025,18 +8229,32 @@
       <c r="F8">
         <v>18</v>
       </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="5"/>
     </row>
-    <row r="11" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="5"/>
@@ -7094,6 +8312,12 @@
       <c r="F5">
         <v>0</v>
       </c>
+      <c r="G5">
+        <v>41</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
@@ -7112,10 +8336,10 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7135,10 +8359,10 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7158,10 +8382,10 @@
         <v>22</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7180,11 +8404,8 @@
       <c r="F9">
         <v>32</v>
       </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
       <c r="H9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7236,6 +8457,212 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC44D17D-F45F-4D39-9789-8C8C574CB691}">
+  <dimension ref="B2:H12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>59</v>
+      </c>
+      <c r="H5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>45912</v>
+      </c>
+      <c r="C6" s="3">
+        <v>45914</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>39</v>
+      </c>
+      <c r="H6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
+        <v>45915</v>
+      </c>
+      <c r="C7" s="3">
+        <v>45918</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
+        <v>45919</v>
+      </c>
+      <c r="C8" s="3">
+        <v>45921</v>
+      </c>
+      <c r="D8" s="4">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
+        <v>45922</v>
+      </c>
+      <c r="C9" s="3">
+        <v>45924</v>
+      </c>
+      <c r="D9" s="4">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="3">
+        <v>45925</v>
+      </c>
+      <c r="C10" s="3">
+        <v>45926</v>
+      </c>
+      <c r="D10" s="5">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>45927</v>
+      </c>
+      <c r="C11" s="3">
+        <v>45928</v>
+      </c>
+      <c r="D11" s="5">
+        <v>19</v>
+      </c>
+      <c r="E11">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>35</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921B85C0-3B10-4CAD-B3EB-3C478ADD0460}">
   <dimension ref="B2:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7289,7 +8716,7 @@
         <v>45914</v>
       </c>
       <c r="D6" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -7298,10 +8725,10 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7321,10 +8748,10 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7335,7 +8762,7 @@
         <v>45921</v>
       </c>
       <c r="D8" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -7344,10 +8771,10 @@
         <v>20</v>
       </c>
       <c r="G8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7358,7 +8785,7 @@
         <v>45924</v>
       </c>
       <c r="D9" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E9">
         <v>23</v>
@@ -7367,10 +8794,10 @@
         <v>24</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7380,20 +8807,12 @@
       <c r="C10" s="3">
         <v>45926</v>
       </c>
-      <c r="D10" s="5">
-        <v>16</v>
-      </c>
+      <c r="D10" s="5"/>
       <c r="E10">
         <v>28</v>
       </c>
       <c r="F10">
         <v>34</v>
-      </c>
-      <c r="G10">
-        <v>10</v>
-      </c>
-      <c r="H10">
-        <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7403,20 +8822,12 @@
       <c r="C11" s="3">
         <v>45928</v>
       </c>
-      <c r="D11" s="5">
-        <v>19</v>
-      </c>
+      <c r="D11" s="5"/>
       <c r="E11">
         <v>33</v>
       </c>
       <c r="F11">
         <v>35</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
